--- a/InputData/plcy-schd/IT/Initial Time.xlsx
+++ b/InputData/plcy-schd/IT/Initial Time.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workfile\EPS China 3.3.1\InputData\plcy-schd\IT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlxl\Desktop\EPS\eps-china2019-smart-trans\InputData\plcy-schd\IT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0AC90B-535F-49E5-87AB-616BC7101286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0DB870-9304-4BD3-AB62-79A7DB6C3F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3749" yWindow="1155" windowWidth="21709" windowHeight="13068" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -158,9 +158,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -198,9 +198,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -233,26 +233,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -285,26 +268,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -479,7 +445,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
@@ -583,7 +549,7 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B1" s="2" t="s">
@@ -595,7 +561,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
   </sheetData>
